--- a/outputs/Bread_tukey_classification_matrix.xlsx
+++ b/outputs/Bread_tukey_classification_matrix.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2550" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2550" uniqueCount="125">
   <si>
     <t>2020 May</t>
   </si>
@@ -341,6 +341,9 @@
   </si>
   <si>
     <t>Minimal</t>
+  </si>
+  <si>
+    <t>No data</t>
   </si>
   <si>
     <t>Alarm</t>
@@ -1213,13 +1216,13 @@
         <v>108</v>
       </c>
       <c r="BU2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BV2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BW2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="3" spans="1:75">
@@ -1227,7 +1230,7 @@
         <v>76</v>
       </c>
       <c r="B3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C3" t="s">
         <v>108</v>
@@ -1251,19 +1254,19 @@
         <v>108</v>
       </c>
       <c r="J3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="K3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="M3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="N3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="O3" t="s">
         <v>108</v>
@@ -1281,70 +1284,70 @@
         <v>108</v>
       </c>
       <c r="T3" t="s">
+        <v>111</v>
+      </c>
+      <c r="U3" t="s">
         <v>110</v>
       </c>
-      <c r="U3" t="s">
-        <v>109</v>
-      </c>
       <c r="V3" t="s">
         <v>108</v>
       </c>
       <c r="W3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="X3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="Y3" t="s">
         <v>108</v>
       </c>
       <c r="Z3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AA3" t="s">
+        <v>111</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>108</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>108</v>
+      </c>
+      <c r="AD3" t="s">
+        <v>108</v>
+      </c>
+      <c r="AE3" t="s">
+        <v>108</v>
+      </c>
+      <c r="AF3" t="s">
         <v>110</v>
       </c>
-      <c r="AB3" t="s">
-        <v>108</v>
-      </c>
-      <c r="AC3" t="s">
-        <v>108</v>
-      </c>
-      <c r="AD3" t="s">
-        <v>108</v>
-      </c>
-      <c r="AE3" t="s">
-        <v>108</v>
-      </c>
-      <c r="AF3" t="s">
-        <v>109</v>
-      </c>
       <c r="AG3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AH3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AI3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AJ3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AK3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AL3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AM3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AN3" t="s">
         <v>108</v>
       </c>
       <c r="AO3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AP3" t="s">
         <v>108</v>
@@ -1359,19 +1362,19 @@
         <v>108</v>
       </c>
       <c r="AT3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AU3" t="s">
         <v>108</v>
       </c>
       <c r="AV3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AW3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AX3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AY3" t="s">
         <v>108</v>
@@ -1398,13 +1401,13 @@
         <v>108</v>
       </c>
       <c r="BG3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BH3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BI3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BJ3" t="s">
         <v>108</v>
@@ -1431,22 +1434,22 @@
         <v>108</v>
       </c>
       <c r="BR3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BS3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BT3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BU3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="BV3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="BW3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="4" spans="1:75">
@@ -1667,13 +1670,13 @@
         <v>108</v>
       </c>
       <c r="BU4" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BV4" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BW4" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="5" spans="1:75">
@@ -1783,10 +1786,10 @@
         <v>108</v>
       </c>
       <c r="AJ5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AK5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AL5" t="s">
         <v>108</v>
@@ -1894,13 +1897,13 @@
         <v>108</v>
       </c>
       <c r="BU5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BV5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="BW5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="6" spans="1:75">
@@ -1962,58 +1965,58 @@
         <v>108</v>
       </c>
       <c r="T6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="U6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="V6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="W6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="X6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="Y6" t="s">
+        <v>111</v>
+      </c>
+      <c r="Z6" t="s">
         <v>110</v>
       </c>
-      <c r="Z6" t="s">
-        <v>109</v>
-      </c>
       <c r="AA6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AB6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AC6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AD6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AE6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AF6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AG6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AH6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AI6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AJ6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AK6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AL6" t="s">
         <v>108</v>
@@ -2121,13 +2124,13 @@
         <v>108</v>
       </c>
       <c r="BU6" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="BV6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="BW6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="7" spans="1:75">
@@ -2348,13 +2351,13 @@
         <v>108</v>
       </c>
       <c r="BU7" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BV7" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BW7" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="8" spans="1:75">
@@ -2407,73 +2410,73 @@
         <v>108</v>
       </c>
       <c r="Q8" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="R8" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="S8" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="T8" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="U8" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="V8" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="W8" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="X8" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="Y8" t="s">
+        <v>111</v>
+      </c>
+      <c r="Z8" t="s">
+        <v>111</v>
+      </c>
+      <c r="AA8" t="s">
+        <v>111</v>
+      </c>
+      <c r="AB8" t="s">
+        <v>111</v>
+      </c>
+      <c r="AC8" t="s">
         <v>110</v>
       </c>
-      <c r="Z8" t="s">
+      <c r="AD8" t="s">
         <v>110</v>
       </c>
-      <c r="AA8" t="s">
+      <c r="AE8" t="s">
         <v>110</v>
       </c>
-      <c r="AB8" t="s">
+      <c r="AF8" t="s">
         <v>110</v>
       </c>
-      <c r="AC8" t="s">
-        <v>109</v>
-      </c>
-      <c r="AD8" t="s">
-        <v>109</v>
-      </c>
-      <c r="AE8" t="s">
-        <v>109</v>
-      </c>
-      <c r="AF8" t="s">
-        <v>109</v>
-      </c>
       <c r="AG8" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AH8" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AI8" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AJ8" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AK8" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AL8" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AM8" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AN8" t="s">
         <v>108</v>
@@ -2575,13 +2578,13 @@
         <v>108</v>
       </c>
       <c r="BU8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="BV8" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="BW8" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="9" spans="1:75">
@@ -2802,13 +2805,13 @@
         <v>108</v>
       </c>
       <c r="BU9" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BV9" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BW9" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="10" spans="1:75">
@@ -3029,13 +3032,13 @@
         <v>108</v>
       </c>
       <c r="BU10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BV10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BW10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="11" spans="1:75">
@@ -3046,7 +3049,7 @@
         <v>108</v>
       </c>
       <c r="C11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D11" t="s">
         <v>108</v>
@@ -3058,13 +3061,13 @@
         <v>108</v>
       </c>
       <c r="G11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="J11" t="s">
         <v>108</v>
@@ -3079,190 +3082,190 @@
         <v>108</v>
       </c>
       <c r="N11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="O11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="P11" t="s">
         <v>108</v>
       </c>
       <c r="Q11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="R11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="S11" t="s">
         <v>108</v>
       </c>
       <c r="T11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="U11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="V11" t="s">
         <v>108</v>
       </c>
       <c r="W11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="X11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="Y11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="Z11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AA11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AB11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AC11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AD11" t="s">
         <v>108</v>
       </c>
       <c r="AE11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AF11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AG11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AH11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AI11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AJ11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AK11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AL11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AM11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AN11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AO11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AP11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AQ11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AR11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AS11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AT11" t="s">
         <v>108</v>
       </c>
       <c r="AU11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AV11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AW11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AX11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AY11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AZ11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BA11" t="s">
         <v>108</v>
       </c>
       <c r="BB11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BC11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BD11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BE11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BF11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BG11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BH11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BI11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BJ11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BK11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BL11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BM11" t="s">
         <v>108</v>
       </c>
       <c r="BN11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BO11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BP11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BQ11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BR11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BS11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BT11" t="s">
         <v>108</v>
       </c>
       <c r="BU11" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BV11" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BW11" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="12" spans="1:75">
@@ -3375,7 +3378,7 @@
         <v>108</v>
       </c>
       <c r="AK12" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AL12" t="s">
         <v>108</v>
@@ -3483,13 +3486,13 @@
         <v>108</v>
       </c>
       <c r="BU12" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BV12" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="BW12" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="13" spans="1:75">
@@ -3710,13 +3713,13 @@
         <v>108</v>
       </c>
       <c r="BU13" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BV13" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BW13" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="14" spans="1:75">
@@ -3937,13 +3940,13 @@
         <v>108</v>
       </c>
       <c r="BU14" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BV14" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BW14" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="15" spans="1:75">
@@ -3969,10 +3972,10 @@
         <v>108</v>
       </c>
       <c r="H15" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I15" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="J15" t="s">
         <v>108</v>
@@ -4002,10 +4005,10 @@
         <v>108</v>
       </c>
       <c r="S15" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="T15" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="U15" t="s">
         <v>108</v>
@@ -4035,16 +4038,16 @@
         <v>108</v>
       </c>
       <c r="AD15" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AE15" t="s">
         <v>108</v>
       </c>
       <c r="AF15" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AG15" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AH15" t="s">
         <v>108</v>
@@ -4071,16 +4074,16 @@
         <v>108</v>
       </c>
       <c r="AP15" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AQ15" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AR15" t="s">
         <v>108</v>
       </c>
       <c r="AS15" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AT15" t="s">
         <v>108</v>
@@ -4107,16 +4110,16 @@
         <v>108</v>
       </c>
       <c r="BB15" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BC15" t="s">
         <v>108</v>
       </c>
       <c r="BD15" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BE15" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BF15" t="s">
         <v>108</v>
@@ -4146,10 +4149,10 @@
         <v>108</v>
       </c>
       <c r="BO15" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BP15" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BQ15" t="s">
         <v>108</v>
@@ -4164,13 +4167,13 @@
         <v>108</v>
       </c>
       <c r="BU15" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BV15" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BW15" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16" spans="1:75">
@@ -4178,226 +4181,226 @@
         <v>89</v>
       </c>
       <c r="B16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C16" t="s">
         <v>108</v>
       </c>
       <c r="D16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="G16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="J16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="K16" t="s">
         <v>108</v>
       </c>
       <c r="L16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="M16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="N16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="O16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="P16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="Q16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="R16" t="s">
         <v>108</v>
       </c>
       <c r="S16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="T16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="U16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="V16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="W16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="X16" t="s">
         <v>108</v>
       </c>
       <c r="Y16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="Z16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AA16" t="s">
         <v>108</v>
       </c>
       <c r="AB16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AC16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AD16" t="s">
         <v>108</v>
       </c>
       <c r="AE16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AF16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AG16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AH16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AI16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AJ16" t="s">
         <v>108</v>
       </c>
       <c r="AK16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AL16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AM16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AN16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AO16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AP16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AQ16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AR16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AS16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AT16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AU16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AV16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AW16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AX16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AY16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AZ16" t="s">
         <v>108</v>
       </c>
       <c r="BA16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BB16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BC16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BD16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BE16" t="s">
         <v>108</v>
       </c>
       <c r="BF16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BG16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BH16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BI16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BJ16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BK16" t="s">
         <v>108</v>
       </c>
       <c r="BL16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BM16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BN16" t="s">
         <v>108</v>
       </c>
       <c r="BO16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BP16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BQ16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BR16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BS16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BT16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BU16" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BV16" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BW16" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="17" spans="1:75">
@@ -4513,7 +4516,7 @@
         <v>108</v>
       </c>
       <c r="AL17" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AM17" t="s">
         <v>108</v>
@@ -4618,13 +4621,13 @@
         <v>108</v>
       </c>
       <c r="BU17" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BV17" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="BW17" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="18" spans="1:75">
@@ -4845,13 +4848,13 @@
         <v>108</v>
       </c>
       <c r="BU18" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BV18" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BW18" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="19" spans="1:75">
@@ -4940,46 +4943,46 @@
         <v>108</v>
       </c>
       <c r="AC19" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AD19" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AE19" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AF19" t="s">
         <v>108</v>
       </c>
       <c r="AG19" t="s">
+        <v>111</v>
+      </c>
+      <c r="AH19" t="s">
+        <v>111</v>
+      </c>
+      <c r="AI19" t="s">
         <v>110</v>
       </c>
-      <c r="AH19" t="s">
+      <c r="AJ19" t="s">
         <v>110</v>
       </c>
-      <c r="AI19" t="s">
-        <v>109</v>
-      </c>
-      <c r="AJ19" t="s">
-        <v>109</v>
-      </c>
       <c r="AK19" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AL19" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AM19" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AN19" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AO19" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AP19" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AQ19" t="s">
         <v>108</v>
@@ -5072,13 +5075,13 @@
         <v>108</v>
       </c>
       <c r="BU19" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="BV19" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="BW19" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="20" spans="1:75">
@@ -5161,13 +5164,13 @@
         <v>108</v>
       </c>
       <c r="AA20" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AB20" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AC20" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AD20" t="s">
         <v>108</v>
@@ -5299,13 +5302,13 @@
         <v>108</v>
       </c>
       <c r="BU20" t="s">
+        <v>113</v>
+      </c>
+      <c r="BV20" t="s">
         <v>112</v>
       </c>
-      <c r="BV20" t="s">
-        <v>111</v>
-      </c>
       <c r="BW20" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="21" spans="1:75">
@@ -5457,11 +5460,11 @@
         <v>108</v>
       </c>
       <c r="AX21" t="s">
+        <v>111</v>
+      </c>
+      <c r="AY21" t="s">
         <v>110</v>
       </c>
-      <c r="AY21" t="s">
-        <v>109</v>
-      </c>
       <c r="AZ21" t="s">
         <v>108</v>
       </c>
@@ -5493,10 +5496,10 @@
         <v>108</v>
       </c>
       <c r="BJ21" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="BK21" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="BL21" t="s">
         <v>108</v>
@@ -5526,13 +5529,13 @@
         <v>108</v>
       </c>
       <c r="BU21" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="BV21" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="BW21" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="22" spans="1:75">
@@ -5753,13 +5756,13 @@
         <v>108</v>
       </c>
       <c r="BU22" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BV22" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BW22" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="23" spans="1:75">
@@ -5980,13 +5983,13 @@
         <v>108</v>
       </c>
       <c r="BU23" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BV23" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BW23" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="24" spans="1:75">
@@ -6102,13 +6105,13 @@
         <v>108</v>
       </c>
       <c r="AL24" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AM24" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AN24" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AO24" t="s">
         <v>108</v>
@@ -6138,13 +6141,13 @@
         <v>108</v>
       </c>
       <c r="AX24" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AY24" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AZ24" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="BA24" t="s">
         <v>108</v>
@@ -6207,13 +6210,13 @@
         <v>108</v>
       </c>
       <c r="BU24" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="BV24" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BW24" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="25" spans="1:75">
@@ -6434,13 +6437,13 @@
         <v>108</v>
       </c>
       <c r="BU25" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BV25" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BW25" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="26" spans="1:75">
@@ -6535,34 +6538,34 @@
         <v>108</v>
       </c>
       <c r="AE26" t="s">
+        <v>111</v>
+      </c>
+      <c r="AF26" t="s">
+        <v>108</v>
+      </c>
+      <c r="AG26" t="s">
+        <v>108</v>
+      </c>
+      <c r="AH26" t="s">
+        <v>108</v>
+      </c>
+      <c r="AI26" t="s">
+        <v>108</v>
+      </c>
+      <c r="AJ26" t="s">
+        <v>108</v>
+      </c>
+      <c r="AK26" t="s">
+        <v>108</v>
+      </c>
+      <c r="AL26" t="s">
         <v>110</v>
       </c>
-      <c r="AF26" t="s">
-        <v>108</v>
-      </c>
-      <c r="AG26" t="s">
-        <v>108</v>
-      </c>
-      <c r="AH26" t="s">
-        <v>108</v>
-      </c>
-      <c r="AI26" t="s">
-        <v>108</v>
-      </c>
-      <c r="AJ26" t="s">
-        <v>108</v>
-      </c>
-      <c r="AK26" t="s">
-        <v>108</v>
-      </c>
-      <c r="AL26" t="s">
-        <v>109</v>
-      </c>
       <c r="AM26" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AN26" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AO26" t="s">
         <v>108</v>
@@ -6661,13 +6664,13 @@
         <v>108</v>
       </c>
       <c r="BU26" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="BV26" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="BW26" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="27" spans="1:75">
@@ -6792,64 +6795,64 @@
         <v>108</v>
       </c>
       <c r="AO27" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AP27" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AQ27" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AR27" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AS27" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AT27" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AU27" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AV27" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AW27" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AX27" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AY27" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AZ27" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="BA27" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="BB27" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="BC27" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="BD27" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="BE27" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="BF27" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="BG27" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="BH27" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="BI27" t="s">
         <v>108</v>
@@ -6888,13 +6891,13 @@
         <v>108</v>
       </c>
       <c r="BU27" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="BV27" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BW27" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="28" spans="1:75">
@@ -7115,13 +7118,13 @@
         <v>108</v>
       </c>
       <c r="BU28" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BV28" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BW28" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="29" spans="1:75">
@@ -7342,13 +7345,13 @@
         <v>108</v>
       </c>
       <c r="BU29" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BV29" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BW29" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="30" spans="1:75">
@@ -7569,13 +7572,13 @@
         <v>108</v>
       </c>
       <c r="BU30" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BV30" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BW30" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="31" spans="1:75">
@@ -7661,13 +7664,13 @@
         <v>108</v>
       </c>
       <c r="AB31" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AC31" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AD31" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AE31" t="s">
         <v>108</v>
@@ -7796,13 +7799,13 @@
         <v>108</v>
       </c>
       <c r="BU31" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BV31" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="BW31" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="32" spans="1:75">
@@ -8023,13 +8026,13 @@
         <v>108</v>
       </c>
       <c r="BU32" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BV32" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BW32" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="33" spans="1:75">
@@ -8250,13 +8253,13 @@
         <v>108</v>
       </c>
       <c r="BU33" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BV33" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BW33" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="34" spans="1:75">
@@ -8339,13 +8342,13 @@
         <v>108</v>
       </c>
       <c r="AA34" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AB34" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AC34" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AD34" t="s">
         <v>108</v>
@@ -8477,13 +8480,13 @@
         <v>108</v>
       </c>
       <c r="BU34" t="s">
+        <v>113</v>
+      </c>
+      <c r="BV34" t="s">
         <v>112</v>
       </c>
-      <c r="BV34" t="s">
-        <v>111</v>
-      </c>
       <c r="BW34" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/Bread_tukey_classification_matrix.xlsx
+++ b/outputs/Bread_tukey_classification_matrix.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2550" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2550" uniqueCount="111">
   <si>
     <t>2020 May</t>
   </si>
@@ -346,49 +346,7 @@
     <t>No data</t>
   </si>
   <si>
-    <t>Alarm</t>
-  </si>
-  <si>
-    <t>Alert</t>
-  </si>
-  <si>
     <t>0%</t>
-  </si>
-  <si>
-    <t>4%</t>
-  </si>
-  <si>
-    <t>23%</t>
-  </si>
-  <si>
-    <t>13%</t>
-  </si>
-  <si>
-    <t>1%</t>
-  </si>
-  <si>
-    <t>8%</t>
-  </si>
-  <si>
-    <t>3%</t>
-  </si>
-  <si>
-    <t>28%</t>
-  </si>
-  <si>
-    <t>6%</t>
-  </si>
-  <si>
-    <t>10%</t>
-  </si>
-  <si>
-    <t>25%</t>
-  </si>
-  <si>
-    <t>32%</t>
-  </si>
-  <si>
-    <t>18%</t>
   </si>
 </sst>
 </file>
@@ -1216,13 +1174,13 @@
         <v>108</v>
       </c>
       <c r="BU2" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="BV2" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="BW2" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="3" spans="1:75">
@@ -1284,10 +1242,10 @@
         <v>108</v>
       </c>
       <c r="T3" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="U3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="V3" t="s">
         <v>108</v>
@@ -1299,13 +1257,13 @@
         <v>109</v>
       </c>
       <c r="Y3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="Z3" t="s">
         <v>109</v>
       </c>
       <c r="AA3" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AB3" t="s">
         <v>108</v>
@@ -1320,10 +1278,10 @@
         <v>108</v>
       </c>
       <c r="AF3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AG3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AH3" t="s">
         <v>109</v>
@@ -1341,13 +1299,13 @@
         <v>109</v>
       </c>
       <c r="AM3" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AN3" t="s">
         <v>108</v>
       </c>
       <c r="AO3" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AP3" t="s">
         <v>108</v>
@@ -1365,7 +1323,7 @@
         <v>109</v>
       </c>
       <c r="AU3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AV3" t="s">
         <v>109</v>
@@ -1410,7 +1368,7 @@
         <v>109</v>
       </c>
       <c r="BJ3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BK3" t="s">
         <v>108</v>
@@ -1443,13 +1401,13 @@
         <v>109</v>
       </c>
       <c r="BU3" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="BV3" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="BW3" t="s">
-        <v>121</v>
+        <v>110</v>
       </c>
     </row>
     <row r="4" spans="1:75">
@@ -1670,13 +1628,13 @@
         <v>108</v>
       </c>
       <c r="BU4" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="BV4" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="BW4" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="5" spans="1:75">
@@ -1786,10 +1744,10 @@
         <v>108</v>
       </c>
       <c r="AJ5" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AK5" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AL5" t="s">
         <v>108</v>
@@ -1897,13 +1855,13 @@
         <v>108</v>
       </c>
       <c r="BU5" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="BV5" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="BW5" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
     </row>
     <row r="6" spans="1:75">
@@ -1965,58 +1923,58 @@
         <v>108</v>
       </c>
       <c r="T6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="U6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="V6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="W6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="X6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Y6" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="Z6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AA6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AB6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AF6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AG6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AH6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AI6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AJ6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AK6" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AL6" t="s">
         <v>108</v>
@@ -2124,13 +2082,13 @@
         <v>108</v>
       </c>
       <c r="BU6" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="BV6" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="BW6" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
     </row>
     <row r="7" spans="1:75">
@@ -2351,13 +2309,13 @@
         <v>108</v>
       </c>
       <c r="BU7" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="BV7" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="BW7" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="8" spans="1:75">
@@ -2410,73 +2368,73 @@
         <v>108</v>
       </c>
       <c r="Q8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="R8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="S8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="T8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="U8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="V8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="W8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="X8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Y8" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="Z8" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AA8" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AB8" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AC8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AF8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AG8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AH8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AI8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AJ8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AK8" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AL8" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AM8" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AN8" t="s">
         <v>108</v>
@@ -2578,13 +2536,13 @@
         <v>108</v>
       </c>
       <c r="BU8" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="BV8" t="s">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="BW8" t="s">
-        <v>123</v>
+        <v>110</v>
       </c>
     </row>
     <row r="9" spans="1:75">
@@ -2805,13 +2763,13 @@
         <v>108</v>
       </c>
       <c r="BU9" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="BV9" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="BW9" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="10" spans="1:75">
@@ -3032,13 +2990,13 @@
         <v>108</v>
       </c>
       <c r="BU10" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="BV10" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="BW10" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="11" spans="1:75">
@@ -3046,7 +3004,7 @@
         <v>84</v>
       </c>
       <c r="B11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C11" t="s">
         <v>109</v>
@@ -3073,13 +3031,13 @@
         <v>108</v>
       </c>
       <c r="K11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L11" t="s">
         <v>108</v>
       </c>
       <c r="M11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="N11" t="s">
         <v>109</v>
@@ -3097,7 +3055,7 @@
         <v>109</v>
       </c>
       <c r="S11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="T11" t="s">
         <v>109</v>
@@ -3259,13 +3217,13 @@
         <v>108</v>
       </c>
       <c r="BU11" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="BV11" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="BW11" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="12" spans="1:75">
@@ -3378,7 +3336,7 @@
         <v>108</v>
       </c>
       <c r="AK12" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AL12" t="s">
         <v>108</v>
@@ -3486,13 +3444,13 @@
         <v>108</v>
       </c>
       <c r="BU12" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="BV12" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="BW12" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
     </row>
     <row r="13" spans="1:75">
@@ -3713,13 +3671,13 @@
         <v>108</v>
       </c>
       <c r="BU13" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="BV13" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="BW13" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="14" spans="1:75">
@@ -3940,13 +3898,13 @@
         <v>108</v>
       </c>
       <c r="BU14" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="BV14" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="BW14" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="15" spans="1:75">
@@ -3966,7 +3924,7 @@
         <v>108</v>
       </c>
       <c r="F15" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="G15" t="s">
         <v>108</v>
@@ -4002,7 +3960,7 @@
         <v>108</v>
       </c>
       <c r="R15" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="S15" t="s">
         <v>109</v>
@@ -4080,7 +4038,7 @@
         <v>109</v>
       </c>
       <c r="AR15" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AS15" t="s">
         <v>109</v>
@@ -4146,7 +4104,7 @@
         <v>108</v>
       </c>
       <c r="BN15" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BO15" t="s">
         <v>109</v>
@@ -4167,13 +4125,13 @@
         <v>108</v>
       </c>
       <c r="BU15" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="BV15" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="BW15" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="16" spans="1:75">
@@ -4208,7 +4166,7 @@
         <v>109</v>
       </c>
       <c r="K16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L16" t="s">
         <v>109</v>
@@ -4247,7 +4205,7 @@
         <v>109</v>
       </c>
       <c r="X16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="Y16" t="s">
         <v>109</v>
@@ -4283,7 +4241,7 @@
         <v>109</v>
       </c>
       <c r="AJ16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AK16" t="s">
         <v>109</v>
@@ -4331,7 +4289,7 @@
         <v>109</v>
       </c>
       <c r="AZ16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BA16" t="s">
         <v>109</v>
@@ -4346,7 +4304,7 @@
         <v>109</v>
       </c>
       <c r="BE16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BF16" t="s">
         <v>109</v>
@@ -4394,13 +4352,13 @@
         <v>109</v>
       </c>
       <c r="BU16" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="BV16" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="BW16" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="17" spans="1:75">
@@ -4423,7 +4381,7 @@
         <v>108</v>
       </c>
       <c r="G17" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H17" t="s">
         <v>108</v>
@@ -4459,7 +4417,7 @@
         <v>108</v>
       </c>
       <c r="S17" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="T17" t="s">
         <v>108</v>
@@ -4495,7 +4453,7 @@
         <v>108</v>
       </c>
       <c r="AE17" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AF17" t="s">
         <v>108</v>
@@ -4516,7 +4474,7 @@
         <v>108</v>
       </c>
       <c r="AL17" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AM17" t="s">
         <v>108</v>
@@ -4531,7 +4489,7 @@
         <v>108</v>
       </c>
       <c r="AQ17" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AR17" t="s">
         <v>108</v>
@@ -4567,7 +4525,7 @@
         <v>108</v>
       </c>
       <c r="BC17" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BD17" t="s">
         <v>108</v>
@@ -4603,7 +4561,7 @@
         <v>108</v>
       </c>
       <c r="BO17" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BP17" t="s">
         <v>108</v>
@@ -4621,13 +4579,13 @@
         <v>108</v>
       </c>
       <c r="BU17" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="BV17" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="BW17" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
     </row>
     <row r="18" spans="1:75">
@@ -4848,13 +4806,13 @@
         <v>108</v>
       </c>
       <c r="BU18" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="BV18" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="BW18" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="19" spans="1:75">
@@ -4943,46 +4901,46 @@
         <v>108</v>
       </c>
       <c r="AC19" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD19" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE19" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AF19" t="s">
         <v>108</v>
       </c>
       <c r="AG19" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AH19" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AI19" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AJ19" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AK19" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AL19" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AM19" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AN19" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AO19" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AP19" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AQ19" t="s">
         <v>108</v>
@@ -5075,13 +5033,13 @@
         <v>108</v>
       </c>
       <c r="BU19" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="BV19" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="BW19" t="s">
-        <v>124</v>
+        <v>110</v>
       </c>
     </row>
     <row r="20" spans="1:75">
@@ -5164,13 +5122,13 @@
         <v>108</v>
       </c>
       <c r="AA20" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AB20" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC20" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD20" t="s">
         <v>108</v>
@@ -5302,13 +5260,13 @@
         <v>108</v>
       </c>
       <c r="BU20" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="BV20" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="BW20" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
     </row>
     <row r="21" spans="1:75">
@@ -5460,10 +5418,10 @@
         <v>108</v>
       </c>
       <c r="AX21" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AY21" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AZ21" t="s">
         <v>108</v>
@@ -5496,10 +5454,10 @@
         <v>108</v>
       </c>
       <c r="BJ21" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="BK21" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="BL21" t="s">
         <v>108</v>
@@ -5529,13 +5487,13 @@
         <v>108</v>
       </c>
       <c r="BU21" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="BV21" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="BW21" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
     </row>
     <row r="22" spans="1:75">
@@ -5756,13 +5714,13 @@
         <v>108</v>
       </c>
       <c r="BU22" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="BV22" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="BW22" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="23" spans="1:75">
@@ -5983,13 +5941,13 @@
         <v>108</v>
       </c>
       <c r="BU23" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="BV23" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="BW23" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="24" spans="1:75">
@@ -6105,13 +6063,13 @@
         <v>108</v>
       </c>
       <c r="AL24" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AM24" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AN24" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AO24" t="s">
         <v>108</v>
@@ -6141,13 +6099,13 @@
         <v>108</v>
       </c>
       <c r="AX24" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AY24" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AZ24" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BA24" t="s">
         <v>108</v>
@@ -6210,13 +6168,13 @@
         <v>108</v>
       </c>
       <c r="BU24" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="BV24" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="BW24" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
     </row>
     <row r="25" spans="1:75">
@@ -6437,13 +6395,13 @@
         <v>108</v>
       </c>
       <c r="BU25" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="BV25" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="BW25" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="26" spans="1:75">
@@ -6538,7 +6496,7 @@
         <v>108</v>
       </c>
       <c r="AE26" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AF26" t="s">
         <v>108</v>
@@ -6559,13 +6517,13 @@
         <v>108</v>
       </c>
       <c r="AL26" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AM26" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AN26" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AO26" t="s">
         <v>108</v>
@@ -6664,13 +6622,13 @@
         <v>108</v>
       </c>
       <c r="BU26" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="BV26" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="BW26" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
     </row>
     <row r="27" spans="1:75">
@@ -6795,64 +6753,64 @@
         <v>108</v>
       </c>
       <c r="AO27" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AP27" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AQ27" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AR27" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AS27" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AT27" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AU27" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AV27" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AW27" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AX27" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AY27" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AZ27" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BA27" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BB27" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BC27" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BD27" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BE27" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BF27" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BG27" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BH27" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BI27" t="s">
         <v>108</v>
@@ -6891,13 +6849,13 @@
         <v>108</v>
       </c>
       <c r="BU27" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="BV27" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="BW27" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
     </row>
     <row r="28" spans="1:75">
@@ -7118,13 +7076,13 @@
         <v>108</v>
       </c>
       <c r="BU28" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="BV28" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="BW28" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="29" spans="1:75">
@@ -7345,13 +7303,13 @@
         <v>108</v>
       </c>
       <c r="BU29" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="BV29" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="BW29" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="30" spans="1:75">
@@ -7572,13 +7530,13 @@
         <v>108</v>
       </c>
       <c r="BU30" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="BV30" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="BW30" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="31" spans="1:75">
@@ -7664,13 +7622,13 @@
         <v>108</v>
       </c>
       <c r="AB31" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AC31" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AD31" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AE31" t="s">
         <v>108</v>
@@ -7799,13 +7757,13 @@
         <v>108</v>
       </c>
       <c r="BU31" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="BV31" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="BW31" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
     </row>
     <row r="32" spans="1:75">
@@ -8026,13 +7984,13 @@
         <v>108</v>
       </c>
       <c r="BU32" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="BV32" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="BW32" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="33" spans="1:75">
@@ -8253,13 +8211,13 @@
         <v>108</v>
       </c>
       <c r="BU33" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="BV33" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="BW33" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="34" spans="1:75">
@@ -8342,13 +8300,13 @@
         <v>108</v>
       </c>
       <c r="AA34" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AB34" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC34" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD34" t="s">
         <v>108</v>
@@ -8480,13 +8438,13 @@
         <v>108</v>
       </c>
       <c r="BU34" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="BV34" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="BW34" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/Bread_tukey_classification_matrix.xlsx
+++ b/outputs/Bread_tukey_classification_matrix.xlsx
@@ -340,7 +340,7 @@
     <t>Zabul</t>
   </si>
   <si>
-    <t>Minimal</t>
+    <t>No concern</t>
   </si>
   <si>
     <t>No data</t>
